--- a/assets/infobasica/planilhas/aula20_nivel2.xlsx
+++ b/assets/infobasica/planilhas/aula20_nivel2.xlsx
@@ -550,7 +550,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>°C → °F: =SEQUÊNCIA(11; 1; 0; 10) em A2 e =A29/5+32 em B2.</t>
+          <t>°C → °F: =SEQUÊNCIA(11; 1; 0; 10) em A2 e =A2*9/5+32 em B2.</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
